--- a/snapshots/shortlist_snapshot_2026-09-20.xlsx
+++ b/snapshots/shortlist_snapshot_2026-09-20.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Captured 2026-09-20 23:03 UTC, before batch market-cap/GM update</t>
+          <t>Captured 2026-09-20 23:18 UTC, before batch market-cap/GM update</t>
         </is>
       </c>
     </row>
